--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486343_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486343_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2639</v>
+        <v>5.759</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1656</v>
+        <v>2.3833</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0983</v>
+        <v>3.3757</v>
       </c>
       <c r="G2" t="n">
         <v>3.6594</v>
@@ -610,13 +610,13 @@
         <v>3.0451</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1271</v>
+        <v>0.6222</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4937</v>
+        <v>0.7114</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3666</v>
+        <v>-0.0892</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. LUNDQVIST</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1964</v>
+        <v>4.9643</v>
       </c>
       <c r="E3" t="n">
-        <v>3.516</v>
+        <v>4.7744</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6804</v>
+        <v>0.1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6071</v>
+        <v>2.9661</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4399</v>
+        <v>1.0735</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.8328</v>
+        <v>1.8925</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2334</v>
+        <v>2.7884</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4303</v>
+        <v>0.876</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.1969</v>
+        <v>1.9125</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3737</v>
+        <v>0.1776</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0096</v>
+        <v>0.1976</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6359</v>
+        <v>-0.0199</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1973</v>
+        <v>-0.024</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0227</v>
+        <v>-0.274</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1746</v>
+        <v>0.2499</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8695</v>
+        <v>0.9347</v>
       </c>
       <c r="W3" t="n">
         <v>2.2599</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3904</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>K. LUNDQVIST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.841</v>
+        <v>4.5066</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7744</v>
+        <v>2.7337</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06660000000000001</v>
+        <v>1.7729</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9661</v>
+        <v>0.6071</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0735</v>
+        <v>3.4399</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8925</v>
+        <v>-2.8328</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7884</v>
+        <v>0.2334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.876</v>
+        <v>2.4303</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9125</v>
+        <v>-2.1969</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1776</v>
+        <v>0.3737</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1976</v>
+        <v>1.0096</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0199</v>
+        <v>-0.6359</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1473</v>
+        <v>0.5074</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.274</v>
+        <v>0.2403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1267</v>
+        <v>0.2671</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>1.8695</v>
       </c>
       <c r="W4" t="n">
         <v>2.2599</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.653</v>
+        <v>2.588</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3003</v>
+        <v>1.993</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9533</v>
+        <v>0.5949</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5277</v>
+        <v>0.8011</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7046</v>
+        <v>1.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1769</v>
+        <v>-0.2574</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2035</v>
+        <v>1.6529</v>
       </c>
       <c r="K5" t="n">
-        <v>3.127</v>
+        <v>1.4234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3242</v>
+        <v>-0.8519</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5776</v>
+        <v>-0.365</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2534</v>
+        <v>-0.4869</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.495</v>
+        <v>0.3503</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1286</v>
+        <v>0.3401</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3664</v>
+        <v>0.0102</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4997</v>
+        <v>0.3491</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6265</v>
+        <v>2.2065</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2165</v>
+        <v>0.0276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.41</v>
+        <v>2.1789</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8011</v>
+        <v>0.0738</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0585</v>
+        <v>0.5169</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2574</v>
+        <v>-0.443</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6529</v>
+        <v>0.45</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4234</v>
+        <v>0.2372</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2295</v>
+        <v>0.2128</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8519</v>
+        <v>-0.3762</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.365</v>
+        <v>0.2796</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>-0.6558</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3889</v>
+        <v>1.0674</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5636</v>
+        <v>0.4699</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1747</v>
+        <v>0.5975</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3491</v>
+        <v>0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4954</v>
+        <v>2.1916</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0842</v>
+        <v>0.8656</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5796</v>
+        <v>1.326</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0738</v>
+        <v>-0.215</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5169</v>
+        <v>1.3078</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.443</v>
+        <v>-1.5228</v>
       </c>
       <c r="J7" t="n">
-        <v>0.45</v>
+        <v>-0.0747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2372</v>
+        <v>1.2592</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2128</v>
+        <v>-1.3339</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3762</v>
+        <v>-0.1403</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2796</v>
+        <v>0.0486</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6558</v>
+        <v>-0.1889</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3563</v>
+        <v>0.5366</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3581</v>
+        <v>0.3329</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9982</v>
+        <v>0.2037</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8949</v>
+        <v>2.1791</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7539</v>
+        <v>-0.1886</v>
       </c>
       <c r="F8" t="n">
-        <v>1.141</v>
+        <v>2.3676</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.215</v>
+        <v>3.5277</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3078</v>
+        <v>3.7046</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5228</v>
+        <v>-0.1769</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0747</v>
+        <v>3.2035</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2592</v>
+        <v>3.127</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3339</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1403</v>
+        <v>0.3242</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0486</v>
+        <v>0.5776</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1889</v>
+        <v>-0.2534</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
         <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2399</v>
+        <v>1.0211</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2211</v>
+        <v>0.2403</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0187</v>
+        <v>0.7808</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.4997</v>
       </c>
       <c r="W8" t="n">
-        <v>1.695</v>
+        <v>-0.3698</v>
       </c>
       <c r="X8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8462</v>
+        <v>2.0081</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0903</v>
+        <v>1.3139</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7558</v>
+        <v>0.6942</v>
       </c>
       <c r="G9" t="n">
         <v>3.2265</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3374</v>
+        <v>0.4993</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1406</v>
+        <v>0.3641</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1968</v>
+        <v>0.1352</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1952</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4962</v>
+        <v>0.766</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1467</v>
+        <v>0.833</v>
       </c>
       <c r="F10" t="n">
-        <v>0.643</v>
+        <v>-0.067</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2992</v>
+        <v>-2.8957</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2888</v>
+        <v>-1.4263</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0103</v>
+        <v>-1.4694</v>
       </c>
       <c r="J10" t="n">
-        <v>0.206</v>
+        <v>-2.039</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0912</v>
+        <v>-1.5234</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1147</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.8567</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1976</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1044</v>
+        <v>-0.9539</v>
       </c>
       <c r="P10" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3032</v>
+        <v>-0.143</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.548</v>
+        <v>-0.5179</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2448</v>
+        <v>0.3749</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3698</v>
+        <v>2.0647</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>3.3899</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2959</v>
+        <v>0.5155</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6095</v>
+        <v>-0.035</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3135</v>
+        <v>0.5505</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8957</v>
+        <v>0.2992</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4263</v>
+        <v>0.2888</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4694</v>
+        <v>0.0103</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.039</v>
+        <v>0.206</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5234</v>
+        <v>0.0912</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.1147</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8567</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1976</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9539</v>
+        <v>-0.1044</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6131</v>
+        <v>-0.2839</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.4362</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1283</v>
+        <v>0.1523</v>
       </c>
       <c r="V11" t="n">
-        <v>2.0647</v>
+        <v>-0.3698</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3899</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1677</v>
+        <v>0.4951</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3883</v>
+        <v>-1.9413</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2206</v>
+        <v>2.4364</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5411</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4967</v>
+        <v>0.1661</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2568</v>
+        <v>0.4726</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2189</v>
+        <v>-0.9569</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6112</v>
+        <v>-2.1641</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3922</v>
+        <v>1.2073</v>
       </c>
       <c r="G13" t="n">
         <v>1.1856</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5138</v>
+        <v>-0.2518</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3766</v>
+        <v>0.1917</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5857</v>
@@ -1501,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.2228</v>
+        <v>27.2229</v>
       </c>
       <c r="E14" t="n">
         <v>10.5955</v>
@@ -1516,7 +1516,7 @@
         <v>13.0174</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3228</v>
+        <v>-0.3227999999999991</v>
       </c>
       <c r="J14" t="n">
         <v>14.867</v>
@@ -1531,13 +1531,13 @@
         <v>-2.1724</v>
       </c>
       <c r="N14" t="n">
-        <v>2.051099999999999</v>
+        <v>2.0511</v>
       </c>
       <c r="O14" t="n">
         <v>-4.2236</v>
       </c>
       <c r="P14" t="n">
-        <v>5.437600000000001</v>
+        <v>5.4376</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.3129</v>
@@ -1546,28 +1546,28 @@
         <v>21.7508</v>
       </c>
       <c r="S14" t="n">
-        <v>4.0678</v>
+        <v>4.067699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7211</v>
+        <v>0.7210999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3466</v>
+        <v>3.3467</v>
       </c>
       <c r="V14" t="n">
-        <v>5.022799999999999</v>
+        <v>5.0228</v>
       </c>
       <c r="W14" t="n">
         <v>11.3203</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.297599999999999</v>
+        <v>-6.2976</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1323</v>
+        <v>-0.1829</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1239</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4044</v>
+        <v>1.5173</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3437</v>
+        <v>-0.949</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0606</v>
+        <v>2.4663</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6183</v>
+        <v>2.6171</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7696</v>
+        <v>0.1309</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1514</v>
+        <v>2.4862</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0226</v>
+        <v>-1.0998</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1134</v>
+        <v>-1.0799</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9093</v>
+        <v>-0.0199</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4093</v>
+        <v>-0.2397</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4627</v>
+        <v>-0.3749</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0534</v>
+        <v>0.1352</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0477</v>
+        <v>-1.243</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3082</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3422</v>
+        <v>-0.2518</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4211</v>
+        <v>-0.4349</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7633</v>
+        <v>0.1831</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6541</v>
+        <v>-1.4044</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.3437</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2686</v>
+        <v>-1.0606</v>
       </c>
       <c r="J16" t="n">
-        <v>1.224</v>
+        <v>0.6183</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.7696</v>
       </c>
       <c r="L16" t="n">
-        <v>1.224</v>
+        <v>-0.1514</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5698</v>
+        <v>-2.0226</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.1134</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0446</v>
+        <v>-0.9093</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1336</v>
+        <v>0.0252</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1971</v>
+        <v>-0.0961</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0635</v>
+        <v>0.1214</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.13</v>
+        <v>-1.0477</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5683</v>
+        <v>-0.4668</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3799</v>
+        <v>1.0858</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1884</v>
+        <v>-1.5526</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5173</v>
+        <v>0.6541</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.949</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4663</v>
+        <v>1.2686</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6171</v>
+        <v>1.224</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1309</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4862</v>
+        <v>1.224</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0998</v>
+        <v>-0.5698</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0799</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0199</v>
+        <v>0.0446</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6251</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>-0.1382</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1968</v>
+        <v>0.1472</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.243</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.243</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.896</v>
+        <v>-1.0501</v>
       </c>
       <c r="E18" t="n">
         <v>-0.9443</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0483</v>
+        <v>-0.1058</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2042</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3082</v>
+        <v>0.1541</v>
       </c>
       <c r="T18" t="n">
         <v>-0.274</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.4281</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1576</v>
+        <v>-1.8121</v>
       </c>
       <c r="E19" t="n">
-        <v>1.082</v>
+        <v>0.9702</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2395</v>
+        <v>-2.7823</v>
       </c>
       <c r="G19" t="n">
         <v>0.8255</v>
@@ -1936,13 +1936,13 @@
         <v>2.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9385</v>
+        <v>-0.593</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4879</v>
+        <v>-0.5996</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4506</v>
+        <v>0.0066</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7395</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.987</v>
+        <v>-2.3883</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.616</v>
+        <v>-1.9454</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.371</v>
+        <v>-0.4428</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6606</v>
@@ -2014,13 +2014,13 @@
         <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2813</v>
+        <v>-0.6826</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3014</v>
+        <v>-0.6309</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0202</v>
+        <v>-0.0517</v>
       </c>
       <c r="V20" t="n">
         <v>1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0405</v>
+        <v>-3.0797</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1533</v>
+        <v>-3.7062</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1127</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3634</v>
@@ -2092,13 +2092,13 @@
         <v>2.8276</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7572</v>
+        <v>-0.7964</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0959</v>
+        <v>-0.6489</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6613</v>
+        <v>-0.1475</v>
       </c>
       <c r="V21" t="n">
         <v>2.7326</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7064</v>
+        <v>-3.9139</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.713</v>
+        <v>-1.3777</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9935</v>
+        <v>-2.5362</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7528</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0635</v>
+        <v>-0.271</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.822</v>
+        <v>-0.4867</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2415</v>
+        <v>0.2157</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8902</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.685</v>
+        <v>-6.0145</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9462</v>
+        <v>-4.3898</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7387</v>
+        <v>-1.6247</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.0997</v>
+        <v>-1.2066</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4733</v>
+        <v>-1.1922</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6264</v>
+        <v>-0.0143</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.328</v>
+        <v>-0.9547</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1439</v>
+        <v>-0.7268</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1841</v>
+        <v>-0.2279</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7716</v>
+        <v>-0.2519</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3293</v>
+        <v>-0.4654</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4423</v>
+        <v>0.2136</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.87</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4801</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>2.6101</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9419999999999999</v>
+        <v>-0.2376</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2762</v>
+        <v>-0.3677</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3342</v>
+        <v>0.1301</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6573</v>
+        <v>-2.1777</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5857</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.243</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9721</v>
+        <v>-6.5726</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5015</v>
+        <v>-5.9521</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4706</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2066</v>
+        <v>-5.0997</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1922</v>
+        <v>-3.4733</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0143</v>
+        <v>-1.6264</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9547</v>
+        <v>-3.328</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7268</v>
+        <v>-2.1439</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2279</v>
+        <v>-1.1841</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2519</v>
+        <v>-1.7716</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4654</v>
+        <v>-1.3293</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2136</v>
+        <v>-0.4423</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3926</v>
+        <v>-0.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2626</v>
+        <v>-3.4801</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1953</v>
+        <v>0.0544</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4795</v>
+        <v>0.2704</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2842</v>
+        <v>-0.216</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1777</v>
+        <v>-0.6573</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1952</v>
+        <v>0.5857</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3729</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-27.2228</v>
+        <v>-25.7327</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.6272</v>
+        <v>-16.6273</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.5956</v>
+        <v>-9.1053</v>
       </c>
       <c r="G25" t="n">
         <v>-12.6948</v>
@@ -2404,16 +2404,16 @@
         <v>16.3131</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.067799999999999</v>
+        <v>-2.5776</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.346699999999999</v>
+        <v>-3.3466</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7211000000000001</v>
+        <v>0.7690999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.0228</v>
+        <v>-5.022800000000001</v>
       </c>
       <c r="W25" t="n">
         <v>6.2976</v>
